--- a/tests-artifacts/api_test_report.xlsx
+++ b/tests-artifacts/api_test_report.xlsx
@@ -415,6 +415,15 @@
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -482,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Received JSON number=0.3419885160461056.</t>
+          <t>Received JSON number=0.3109308900086357.</t>
         </is>
       </c>
     </row>

--- a/tests-artifacts/api_test_report.xlsx
+++ b/tests-artifacts/api_test_report.xlsx
@@ -413,17 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -478,7 +469,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Generate a random number and validate its numeric half-open interval.</t>
+          <t>Existing random-number API</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -491,7 +482,40 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Received JSON number=0.3109308900086357.</t>
+          <t>Live HTTP request succeeded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>/generate-letter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Public random uppercase English-letter API</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Live HTTP request succeeded.</t>
         </is>
       </c>
     </row>
